--- a/outputs/Block4_Lowest_Sensitivity_v12.xlsx
+++ b/outputs/Block4_Lowest_Sensitivity_v12.xlsx
@@ -118,22 +118,22 @@
     <t>RHouSafResH (&gt;10%)</t>
   </si>
   <si>
+    <t>DSenLeanResH  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
     <t>DHouTiltResLR (&lt;=1%)</t>
   </si>
   <si>
-    <t>DSenLeanResH  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
     <t>DHouTiltResH (&lt;=1%)</t>
   </si>
   <si>
     <t>RHouSafResLD (&gt;10%)</t>
   </si>
   <si>
+    <t>DSenLeanResLR  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
     <t>RHouTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>DHouLikResLR (&gt;5%&lt;=10%)</t>
   </si>
   <si>
     <t>Senate Buckets</t>
@@ -645,10 +645,10 @@
         <v>42</v>
       </c>
       <c r="P2">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="Q2">
-        <v>1.141286249557361</v>
+        <v>1.149511773378675</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -657,10 +657,10 @@
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.141286249557361</v>
+        <v>0.1495117733786751</v>
       </c>
       <c r="U2">
-        <v>-0.141286249557361</v>
+        <v>-0.1495117733786751</v>
       </c>
       <c r="V2" t="s">
         <v>6</v>
@@ -689,25 +689,25 @@
         <v>41</v>
       </c>
       <c r="C3">
-        <v>15.048</v>
+        <v>15.328</v>
       </c>
       <c r="D3">
-        <v>14.824</v>
+        <v>14.864</v>
       </c>
       <c r="E3">
-        <v>15.00521451603779</v>
+        <v>15.0529980979447</v>
       </c>
       <c r="F3">
         <v>14.2</v>
       </c>
       <c r="G3">
-        <v>14.93988810988627</v>
+        <v>15.10405394190727</v>
       </c>
       <c r="J3" t="s">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>15.00521451603779</v>
+        <v>15.0529980979447</v>
       </c>
       <c r="L3">
         <v>6.129350049043507</v>
@@ -722,10 +722,10 @@
         <v>42</v>
       </c>
       <c r="P3">
-        <v>14.85295632081913</v>
+        <v>14.78112560442925</v>
       </c>
       <c r="Q3">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R3">
         <v>15</v>
@@ -734,34 +734,34 @@
         <v>43</v>
       </c>
       <c r="T3">
-        <v>-0.152258195218657</v>
+        <v>-0.2718724935154491</v>
       </c>
       <c r="U3">
-        <v>0.1470436791808698</v>
+        <v>0.2188743955707473</v>
       </c>
       <c r="V3" t="s">
         <v>6</v>
       </c>
       <c r="W3">
-        <v>14.93988810988627</v>
+        <v>15.10405394190727</v>
       </c>
       <c r="X3">
-        <v>0.06532640615151664</v>
+        <v>0.05105584396257257</v>
       </c>
       <c r="Y3">
-        <v>0.00521451603778722</v>
+        <v>0.05299809794470178</v>
       </c>
       <c r="Z3">
-        <v>0.01065796628171219</v>
+        <v>0.00832973211744366</v>
       </c>
       <c r="AA3">
-        <v>0.0008507453475594778</v>
+        <v>0.008646609758072507</v>
       </c>
       <c r="AB3">
         <v>0.972912706197382</v>
       </c>
       <c r="AC3">
-        <v>99.2800601772977</v>
+        <v>99.1594882890594</v>
       </c>
       <c r="AD3" t="s">
         <v>44</v>
@@ -775,25 +775,25 @@
         <v>41</v>
       </c>
       <c r="C4">
-        <v>13.316</v>
+        <v>13.532</v>
       </c>
       <c r="D4">
-        <v>12.472</v>
+        <v>12.556</v>
       </c>
       <c r="E4">
-        <v>12.98388364583827</v>
+        <v>13.3559567781861</v>
       </c>
       <c r="F4">
         <v>11.8</v>
       </c>
       <c r="G4">
-        <v>12.9086498426072</v>
+        <v>13.06094105021875</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>12.98388364583827</v>
+        <v>13.3559567781861</v>
       </c>
       <c r="L4">
         <v>3.125306797245826</v>
@@ -808,10 +808,10 @@
         <v>42</v>
       </c>
       <c r="P4">
-        <v>12.85213593315269</v>
+        <v>13.11473458118962</v>
       </c>
       <c r="Q4">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R4">
         <v>13</v>
@@ -820,34 +820,34 @@
         <v>43</v>
       </c>
       <c r="T4">
-        <v>-0.1317477126855753</v>
+        <v>-0.2412221969964765</v>
       </c>
       <c r="U4">
-        <v>0.1478640668473066</v>
+        <v>-0.1147345811896248</v>
       </c>
       <c r="V4" t="s">
         <v>6</v>
       </c>
       <c r="W4">
-        <v>12.9086498426072</v>
+        <v>13.06094105021875</v>
       </c>
       <c r="X4">
-        <v>0.07523380323107176</v>
+        <v>0.2950157279673533</v>
       </c>
       <c r="Y4">
-        <v>0.01611635416173129</v>
+        <v>0.3559567781861013</v>
       </c>
       <c r="Z4">
-        <v>0.02407245371794266</v>
+        <v>0.09439576563406053</v>
       </c>
       <c r="AA4">
-        <v>0.005156727069462051</v>
+        <v>0.1138949873656525</v>
       </c>
       <c r="AB4">
         <v>0.6511055827595471</v>
       </c>
       <c r="AC4">
-        <v>98.2699453837879</v>
+        <v>90.37337437343564</v>
       </c>
       <c r="AD4" t="s">
         <v>44</v>
@@ -861,25 +861,25 @@
         <v>41</v>
       </c>
       <c r="C5">
-        <v>172.1</v>
+        <v>171.868</v>
       </c>
       <c r="D5">
-        <v>175.156</v>
+        <v>174.552</v>
       </c>
       <c r="E5">
-        <v>175.5898630732044</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="F5">
         <v>172.6</v>
       </c>
       <c r="G5">
-        <v>173.5749550722659</v>
+        <v>173.1634121118985</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>175.5898630732044</v>
+        <v>175.5728436009487</v>
       </c>
       <c r="L5">
         <v>24.70132137894479</v>
@@ -894,49 +894,49 @@
         <v>42</v>
       </c>
       <c r="P5">
-        <v>173.8081494148196</v>
+        <v>172.4018190334305</v>
       </c>
       <c r="Q5">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R5">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>-1.781713658384717</v>
+        <v>-3.171024567518231</v>
       </c>
       <c r="U5">
-        <v>0.1918505851803616</v>
+        <v>-0.4018190334304563</v>
       </c>
       <c r="V5" t="s">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>173.5749550722659</v>
+        <v>173.1634121118985</v>
       </c>
       <c r="X5">
-        <v>2.014908000938448</v>
+        <v>2.409431489050235</v>
       </c>
       <c r="Y5">
-        <v>1.589863073204356</v>
+        <v>3.572843600948687</v>
       </c>
       <c r="Z5">
-        <v>0.08157085890376452</v>
+        <v>0.09754261531547112</v>
       </c>
       <c r="AA5">
-        <v>0.06436348277948976</v>
+        <v>0.1446418005797111</v>
       </c>
       <c r="AB5">
         <v>1.320926276948919</v>
       </c>
       <c r="AC5">
-        <v>92.72349650896915</v>
+        <v>89.22335706647648</v>
       </c>
       <c r="AD5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -944,85 +944,85 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6">
-        <v>1.412</v>
+        <v>1.168</v>
       </c>
       <c r="D6">
-        <v>1.808</v>
+        <v>1.328</v>
       </c>
       <c r="E6">
-        <v>1.699906626866217</v>
+        <v>1.138895095514905</v>
       </c>
       <c r="F6">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="G6">
-        <v>1.603126377165344</v>
+        <v>1.243204011857575</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>1.699906626866217</v>
+        <v>1.138895095514905</v>
       </c>
       <c r="L6">
-        <v>1.746417103282563</v>
+        <v>0.9319718387197466</v>
       </c>
       <c r="M6">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N6">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="O6" t="s">
         <v>42</v>
       </c>
       <c r="P6">
-        <v>1.717926703142854</v>
+        <v>0.9726626509918868</v>
       </c>
       <c r="Q6">
-        <v>1.010600627112006</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.01802007627663649</v>
+        <v>-0.1662324445230186</v>
       </c>
       <c r="U6">
-        <v>0.2820732968571464</v>
+        <v>0.02733734900811324</v>
       </c>
       <c r="V6" t="s">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>1.603126377165344</v>
+        <v>1.243204011857575</v>
       </c>
       <c r="X6">
-        <v>0.09678024970087273</v>
+        <v>0.10430891634267</v>
       </c>
       <c r="Y6">
-        <v>0.3000933731337829</v>
+        <v>0.1388950955149053</v>
       </c>
       <c r="Z6">
-        <v>0.05541645779748992</v>
+        <v>0.1119228199920285</v>
       </c>
       <c r="AA6">
-        <v>0.1718337346615124</v>
+        <v>0.1490335756343304</v>
       </c>
       <c r="AB6">
-        <v>0.7593117840358968</v>
+        <v>1.035524265244163</v>
       </c>
       <c r="AC6">
-        <v>90.83163983910151</v>
+        <v>88.25749324682307</v>
       </c>
       <c r="AD6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -1030,85 +1030,85 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7">
-        <v>1.164</v>
+        <v>1.344</v>
       </c>
       <c r="D7">
-        <v>1.34</v>
+        <v>1.788</v>
       </c>
       <c r="E7">
-        <v>1.234402433809649</v>
+        <v>1.473024875335867</v>
       </c>
       <c r="F7">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="G7">
-        <v>1.246724413043333</v>
+        <v>1.558293210761144</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>1.234402433809649</v>
+        <v>1.473024875335867</v>
       </c>
       <c r="L7">
-        <v>0.9319718387197466</v>
+        <v>1.746417103282563</v>
       </c>
       <c r="M7">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N7">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="s">
         <v>42</v>
       </c>
       <c r="P7">
-        <v>1.06279383028951</v>
+        <v>1.501280428022223</v>
       </c>
       <c r="Q7">
-        <v>0.8609783982760665</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>-0.1716086035201392</v>
+        <v>0.02825555268635682</v>
       </c>
       <c r="U7">
-        <v>-0.06279383028951013</v>
+        <v>0.4987195719777766</v>
       </c>
       <c r="V7" t="s">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>1.246724413043333</v>
+        <v>1.558293210761144</v>
       </c>
       <c r="X7">
-        <v>0.01232197923368372</v>
+        <v>0.08526833542527745</v>
       </c>
       <c r="Y7">
-        <v>0.2344024338096493</v>
+        <v>0.5269751246641334</v>
       </c>
       <c r="Z7">
-        <v>0.0132214072590546</v>
+        <v>0.04882472535627785</v>
       </c>
       <c r="AA7">
-        <v>0.2515123569953024</v>
+        <v>0.3017464291168656</v>
       </c>
       <c r="AB7">
-        <v>1.035524265244163</v>
+        <v>0.7593117840358968</v>
       </c>
       <c r="AC7">
-        <v>90.78980016577228</v>
+        <v>87.16674245626311</v>
       </c>
       <c r="AD7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1119,25 +1119,25 @@
         <v>41</v>
       </c>
       <c r="C8">
-        <v>1.128</v>
+        <v>1.076</v>
       </c>
       <c r="D8">
-        <v>1.252</v>
+        <v>1.236</v>
       </c>
       <c r="E8">
-        <v>1.026071324842432</v>
+        <v>0.966548112280941</v>
       </c>
       <c r="F8">
         <v>1.4</v>
       </c>
       <c r="G8">
-        <v>1.187847653455815</v>
+        <v>1.153222778652665</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>1.026071324842432</v>
+        <v>0.966548112280941</v>
       </c>
       <c r="L8">
         <v>0.8200692764238203</v>
@@ -1152,10 +1152,10 @@
         <v>42</v>
       </c>
       <c r="P8">
-        <v>1.036948324347409</v>
+        <v>0.9850884312991284</v>
       </c>
       <c r="Q8">
-        <v>1.010600627112006</v>
+        <v>1.019181992890591</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -1164,34 +1164,34 @@
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.01087699950497645</v>
+        <v>0.01854031901818742</v>
       </c>
       <c r="U8">
-        <v>-0.03694832434740891</v>
+        <v>0.01491156870087162</v>
       </c>
       <c r="V8" t="s">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>1.187847653455815</v>
+        <v>1.153222778652665</v>
       </c>
       <c r="X8">
-        <v>0.1617763286133824</v>
+        <v>0.1866746663717236</v>
       </c>
       <c r="Y8">
-        <v>0.02607132484243246</v>
+        <v>0.03345188771905905</v>
       </c>
       <c r="Z8">
-        <v>0.1972715394470829</v>
+        <v>0.2276328009577183</v>
       </c>
       <c r="AA8">
-        <v>0.03179161272340916</v>
+        <v>0.04079153881357063</v>
       </c>
       <c r="AB8">
         <v>0.7455175240216548</v>
       </c>
       <c r="AC8">
-        <v>86.99204005901876</v>
+        <v>85.02385182059285</v>
       </c>
       <c r="AD8" t="s">
         <v>45</v>
@@ -1205,25 +1205,25 @@
         <v>41</v>
       </c>
       <c r="C9">
-        <v>5.304</v>
+        <v>5.384</v>
       </c>
       <c r="D9">
-        <v>4.316</v>
+        <v>4.436</v>
       </c>
       <c r="E9">
-        <v>4.035405960595082</v>
+        <v>4.289783155551396</v>
       </c>
       <c r="F9">
         <v>4.4</v>
       </c>
       <c r="G9">
-        <v>4.827149341819798</v>
+        <v>4.926455036482963</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>4.035405960595082</v>
+        <v>4.289783155551396</v>
       </c>
       <c r="L9">
         <v>2.858585552684069</v>
@@ -1238,10 +1238,10 @@
         <v>42</v>
       </c>
       <c r="P9">
-        <v>3.994458620063688</v>
+        <v>4.212305297947762</v>
       </c>
       <c r="Q9">
-        <v>0.9898529811049405</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R9">
         <v>4</v>
@@ -1250,34 +1250,34 @@
         <v>43</v>
       </c>
       <c r="T9">
-        <v>-0.04094734053139382</v>
+        <v>-0.07747785760363346</v>
       </c>
       <c r="U9">
-        <v>0.005541379936312207</v>
+        <v>-0.2123052979477622</v>
       </c>
       <c r="V9" t="s">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>4.827149341819798</v>
+        <v>4.926455036482963</v>
       </c>
       <c r="X9">
-        <v>0.7917433812247161</v>
+        <v>0.6366718809315675</v>
       </c>
       <c r="Y9">
-        <v>0.03540596059508161</v>
+        <v>0.2897831555513957</v>
       </c>
       <c r="Z9">
-        <v>0.2769703290780675</v>
+        <v>0.2227226959619118</v>
       </c>
       <c r="AA9">
-        <v>0.01238583206363622</v>
+        <v>0.1013729168536879</v>
       </c>
       <c r="AB9">
         <v>0.6972159884595291</v>
       </c>
       <c r="AC9">
-        <v>83.16315746844765</v>
+        <v>83.50611917578671</v>
       </c>
       <c r="AD9" t="s">
         <v>45</v>
@@ -1288,82 +1288,82 @@
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10">
-        <v>3.692</v>
+        <v>0.6</v>
       </c>
       <c r="D10">
-        <v>3.192</v>
+        <v>0.696</v>
       </c>
       <c r="E10">
-        <v>3.475459163737268</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="G10">
-        <v>3.450678816710424</v>
+        <v>0.6451224071145452</v>
       </c>
       <c r="J10" t="s">
         <v>4</v>
       </c>
       <c r="K10">
-        <v>3.475459163737268</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="L10">
-        <v>0.887818750560327</v>
+        <v>1.559831022862906</v>
       </c>
       <c r="M10">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N10">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="s">
         <v>42</v>
       </c>
       <c r="P10">
-        <v>3.440193613933819</v>
+        <v>0.2767323416308665</v>
       </c>
       <c r="Q10">
-        <v>0.9898529811049405</v>
+        <v>0.8540406002469759</v>
       </c>
       <c r="R10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>-0.03526554980344976</v>
+        <v>-0.04729480830888999</v>
       </c>
       <c r="U10">
-        <v>-0.4401936139338187</v>
+        <v>-0.2767323416308665</v>
       </c>
       <c r="V10" t="s">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>3.450678816710424</v>
+        <v>0.6451224071145452</v>
       </c>
       <c r="X10">
-        <v>0.0247803470268444</v>
+        <v>0.3210952571747887</v>
       </c>
       <c r="Y10">
-        <v>0.4754591637372685</v>
+        <v>0.3240271499397565</v>
       </c>
       <c r="Z10">
-        <v>0.02791149320872625</v>
+        <v>0.2058525907411766</v>
       </c>
       <c r="AA10">
-        <v>0.5355362943587225</v>
+        <v>0.207732212778432</v>
       </c>
       <c r="AB10">
-        <v>0.3551275002241308</v>
+        <v>1.299859185719089</v>
       </c>
       <c r="AC10">
-        <v>81.41748166151876</v>
+        <v>81.34177543201334</v>
       </c>
       <c r="AD10" t="s">
         <v>45</v>
@@ -1377,79 +1377,79 @@
         <v>41</v>
       </c>
       <c r="C11">
-        <v>3.184</v>
+        <v>3.784</v>
       </c>
       <c r="D11">
-        <v>4.004</v>
+        <v>3.252</v>
       </c>
       <c r="E11">
-        <v>1.550377686812013</v>
+        <v>3.656634670288002</v>
       </c>
       <c r="F11">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>3.579766740594905</v>
+        <v>3.527234260979891</v>
       </c>
       <c r="J11" t="s">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>1.550377686812013</v>
+        <v>3.656634670288002</v>
       </c>
       <c r="L11">
-        <v>7.059923274159115</v>
+        <v>0.887818750560327</v>
       </c>
       <c r="M11">
         <v>5.24749619700716</v>
       </c>
       <c r="N11">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="s">
         <v>42</v>
       </c>
       <c r="P11">
-        <v>1.566812662552681</v>
+        <v>3.590592119879259</v>
       </c>
       <c r="Q11">
-        <v>1.010600627112006</v>
+        <v>0.981938980411313</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
       </c>
       <c r="T11">
-        <v>0.01643497574066832</v>
+        <v>-0.06604255040874341</v>
       </c>
       <c r="U11">
-        <v>0.433187337447319</v>
+        <v>0.409407880120741</v>
       </c>
       <c r="V11" t="s">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>3.579766740594905</v>
+        <v>3.527234260979891</v>
       </c>
       <c r="X11">
-        <v>2.029389053782892</v>
+        <v>0.1294004093081114</v>
       </c>
       <c r="Y11">
-        <v>0.4496223131879873</v>
+        <v>0.3433653297119976</v>
       </c>
       <c r="Z11">
-        <v>0.2874519984106493</v>
+        <v>0.1457509308363258</v>
       </c>
       <c r="AA11">
-        <v>0.06368657218042365</v>
+        <v>0.3867516083607045</v>
       </c>
       <c r="AB11">
-        <v>0.9289372729156731</v>
+        <v>0.3551275002241308</v>
       </c>
       <c r="AC11">
-        <v>81.12864354622022</v>
+        <v>79.44532252176565</v>
       </c>
       <c r="AD11" t="s">
         <v>45</v>

--- a/outputs/Block4_Lowest_Sensitivity_v12.xlsx
+++ b/outputs/Block4_Lowest_Sensitivity_v12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="45">
   <si>
     <t>Variable</t>
   </si>
@@ -109,31 +109,31 @@
     <t>RSenLeanResH  (&gt;1&lt;=5%)</t>
   </si>
   <si>
+    <t>DHouLeanResH  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>DHouSafResLR (&gt;10%)</t>
+  </si>
+  <si>
     <t>RHouLikResH (&gt;5%&lt;=10%)</t>
   </si>
   <si>
+    <t>RHouLeanResLD  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>DHouLikResLR (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>RHouTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>RHouTiltResLD (&lt;=1%)</t>
+  </si>
+  <si>
     <t>RHouLeanResH  (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>RHouSafResH (&gt;10%)</t>
-  </si>
-  <si>
-    <t>DSenLeanResH  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>DHouTiltResLR (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>DHouTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>RHouSafResLD (&gt;10%)</t>
-  </si>
-  <si>
-    <t>DSenLeanResLR  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>RHouTiltResH (&lt;=1%)</t>
+    <t>DHouLikResH (&gt;5%&lt;=10%)</t>
   </si>
   <si>
     <t>Senate Buckets</t>
@@ -149,9 +149,6 @@
   </si>
   <si>
     <t>Low sensitivity</t>
-  </si>
-  <si>
-    <t>Moderate-low sensitivity</t>
   </si>
 </sst>
 </file>
@@ -624,7 +621,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="J2" t="s">
         <v>4</v>
@@ -633,10 +630,10 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>2.220446049250313E-17</v>
       </c>
       <c r="M2">
-        <v>1.038416113387647</v>
+        <v>1.101478811702765</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -645,10 +642,10 @@
         <v>42</v>
       </c>
       <c r="P2">
-        <v>1.149511773378675</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="Q2">
-        <v>1.149511773378675</v>
+        <v>1.232268571848568</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -657,21 +654,27 @@
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.1495117733786751</v>
+        <v>0.2322685718485682</v>
       </c>
       <c r="U2">
-        <v>-0.1495117733786751</v>
+        <v>-0.2322685718485682</v>
       </c>
       <c r="V2" t="s">
         <v>6</v>
       </c>
       <c r="W2">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>1.110223024625157E-16</v>
+        <v>0</v>
       </c>
       <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
         <v>0</v>
       </c>
       <c r="AC2">
@@ -689,79 +692,79 @@
         <v>41</v>
       </c>
       <c r="C3">
-        <v>15.328</v>
+        <v>3.828</v>
       </c>
       <c r="D3">
-        <v>14.864</v>
+        <v>6.036</v>
       </c>
       <c r="E3">
-        <v>15.0529980979447</v>
+        <v>4.770944606916803</v>
       </c>
       <c r="F3">
-        <v>14.2</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>15.10405394190727</v>
+        <v>4.844607231094189</v>
       </c>
       <c r="J3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>15.0529980979447</v>
+        <v>4.844607231094189</v>
       </c>
       <c r="L3">
-        <v>6.129350049043507</v>
+        <v>5.084231521849853</v>
       </c>
       <c r="M3">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N3">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="O3" t="s">
         <v>42</v>
       </c>
       <c r="P3">
-        <v>14.78112560442925</v>
+        <v>5.027637971466064</v>
       </c>
       <c r="Q3">
-        <v>0.981938980411313</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>-0.2718724935154491</v>
+        <v>0.1830307403718754</v>
       </c>
       <c r="U3">
-        <v>0.2188743955707473</v>
+        <v>-0.02763797146606439</v>
       </c>
       <c r="V3" t="s">
         <v>6</v>
       </c>
       <c r="W3">
-        <v>15.10405394190727</v>
+        <v>4.844607231094189</v>
       </c>
       <c r="X3">
-        <v>0.05105584396257257</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>0.05299809794470178</v>
+        <v>0.155392768905811</v>
       </c>
       <c r="Z3">
-        <v>0.00832973211744366</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.008646609758072507</v>
+        <v>0.03056366891200751</v>
       </c>
       <c r="AB3">
-        <v>0.972912706197382</v>
+        <v>0.6778975362466471</v>
       </c>
       <c r="AC3">
-        <v>99.1594882890594</v>
+        <v>98.93597283506041</v>
       </c>
       <c r="AD3" t="s">
         <v>44</v>
@@ -775,79 +778,79 @@
         <v>41</v>
       </c>
       <c r="C4">
-        <v>13.532</v>
+        <v>1.748</v>
       </c>
       <c r="D4">
-        <v>12.556</v>
+        <v>3.744</v>
       </c>
       <c r="E4">
-        <v>13.3559567781861</v>
+        <v>-5.9050260855817</v>
       </c>
       <c r="F4">
-        <v>11.8</v>
+        <v>6.8</v>
       </c>
       <c r="G4">
-        <v>13.06094105021875</v>
+        <v>2.666998203471015</v>
       </c>
       <c r="J4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>13.3559567781861</v>
+        <v>2.666998203471015</v>
       </c>
       <c r="L4">
-        <v>3.125306797245826</v>
+        <v>9.299703921130613</v>
       </c>
       <c r="M4">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N4">
-        <v>4.8</v>
+        <v>10.1</v>
       </c>
       <c r="O4" t="s">
         <v>42</v>
       </c>
       <c r="P4">
-        <v>13.11473458118962</v>
+        <v>2.767758209900166</v>
       </c>
       <c r="Q4">
-        <v>0.981938980411313</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R4">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>-0.2412221969964765</v>
+        <v>0.1007600064291512</v>
       </c>
       <c r="U4">
-        <v>-0.1147345811896248</v>
+        <v>0.2322417900998337</v>
       </c>
       <c r="V4" t="s">
         <v>6</v>
       </c>
       <c r="W4">
-        <v>13.06094105021875</v>
+        <v>2.666998203471015</v>
       </c>
       <c r="X4">
-        <v>0.2950157279673533</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>0.3559567781861013</v>
+        <v>0.3330017965289849</v>
       </c>
       <c r="Z4">
-        <v>0.09439576563406053</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>0.1138949873656525</v>
+        <v>0.03580778478036752</v>
       </c>
       <c r="AB4">
-        <v>0.6511055827595471</v>
+        <v>0.9207627644683776</v>
       </c>
       <c r="AC4">
-        <v>90.37337437343564</v>
+        <v>98.75454828619661</v>
       </c>
       <c r="AD4" t="s">
         <v>44</v>
@@ -861,82 +864,82 @@
         <v>41</v>
       </c>
       <c r="C5">
-        <v>171.868</v>
+        <v>14.108</v>
       </c>
       <c r="D5">
-        <v>174.552</v>
+        <v>12.212</v>
       </c>
       <c r="E5">
-        <v>175.5728436009487</v>
+        <v>10.50855707095638</v>
       </c>
       <c r="F5">
-        <v>172.6</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>173.1634121118985</v>
+        <v>13.23504379069086</v>
       </c>
       <c r="J5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>175.5728436009487</v>
+        <v>13.23504379069086</v>
       </c>
       <c r="L5">
-        <v>24.70132137894479</v>
+        <v>5.542668330792591</v>
       </c>
       <c r="M5">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N5">
-        <v>18.7</v>
+        <v>7</v>
       </c>
       <c r="O5" t="s">
         <v>42</v>
       </c>
       <c r="P5">
-        <v>172.4018190334305</v>
+        <v>12.80565286246813</v>
       </c>
       <c r="Q5">
-        <v>0.981938980411313</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R5">
-        <v>172</v>
+        <v>13</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>-3.171024567518231</v>
+        <v>-0.4293909282227268</v>
       </c>
       <c r="U5">
-        <v>-0.4018190334304563</v>
+        <v>0.1943471375318673</v>
       </c>
       <c r="V5" t="s">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>173.1634121118985</v>
+        <v>13.23504379069086</v>
       </c>
       <c r="X5">
-        <v>2.409431489050235</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>3.572843600948687</v>
+        <v>0.2350437906908596</v>
       </c>
       <c r="Z5">
-        <v>0.09754261531547112</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>0.1446418005797111</v>
+        <v>0.04240625212680708</v>
       </c>
       <c r="AB5">
-        <v>1.320926276948919</v>
+        <v>0.7918097615417986</v>
       </c>
       <c r="AC5">
-        <v>89.22335706647648</v>
+        <v>98.52674141152615</v>
       </c>
       <c r="AD5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -944,85 +947,85 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6">
-        <v>1.168</v>
+        <v>10.3</v>
       </c>
       <c r="D6">
-        <v>1.328</v>
+        <v>7.98</v>
       </c>
       <c r="E6">
-        <v>1.138895095514905</v>
+        <v>6.105754884068356</v>
       </c>
       <c r="F6">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="G6">
-        <v>1.243204011857575</v>
+        <v>9.231825735444511</v>
       </c>
       <c r="J6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>1.138895095514905</v>
+        <v>9.231825735444511</v>
       </c>
       <c r="L6">
-        <v>0.9319718387197466</v>
+        <v>5.429823374723132</v>
       </c>
       <c r="M6">
-        <v>1.038416113387647</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N6">
-        <v>0.9</v>
+        <v>7.9</v>
       </c>
       <c r="O6" t="s">
         <v>42</v>
       </c>
       <c r="P6">
-        <v>0.9726626509918868</v>
+        <v>8.932313147165718</v>
       </c>
       <c r="Q6">
-        <v>0.8540406002469759</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>-0.1662324445230186</v>
+        <v>-0.2995125882787928</v>
       </c>
       <c r="U6">
-        <v>0.02733734900811324</v>
+        <v>0.06768685283428155</v>
       </c>
       <c r="V6" t="s">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>1.243204011857575</v>
+        <v>9.231825735444511</v>
       </c>
       <c r="X6">
-        <v>0.10430891634267</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>0.1388950955149053</v>
+        <v>0.2318257354445112</v>
       </c>
       <c r="Z6">
-        <v>0.1119228199920285</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>0.1490335756343304</v>
+        <v>0.04269489437238501</v>
       </c>
       <c r="AB6">
-        <v>1.035524265244163</v>
+        <v>0.6873194145219155</v>
       </c>
       <c r="AC6">
-        <v>88.25749324682307</v>
+        <v>98.51678827132986</v>
       </c>
       <c r="AD6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -1033,82 +1036,82 @@
         <v>41</v>
       </c>
       <c r="C7">
-        <v>1.344</v>
+        <v>1.924</v>
       </c>
       <c r="D7">
-        <v>1.788</v>
+        <v>3.576</v>
       </c>
       <c r="E7">
-        <v>1.473024875335867</v>
+        <v>-3.969061584617776</v>
       </c>
       <c r="F7">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="G7">
-        <v>1.558293210761144</v>
+        <v>2.684613743554167</v>
       </c>
       <c r="J7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>1.473024875335867</v>
+        <v>2.684613743554167</v>
       </c>
       <c r="L7">
-        <v>1.746417103282563</v>
+        <v>7.332928773632203</v>
       </c>
       <c r="M7">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N7">
-        <v>2.3</v>
+        <v>8</v>
       </c>
       <c r="O7" t="s">
         <v>42</v>
       </c>
       <c r="P7">
-        <v>1.501280428022223</v>
+        <v>2.786039270466129</v>
       </c>
       <c r="Q7">
-        <v>1.019181992890591</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.02825555268635682</v>
+        <v>0.1014255269119624</v>
       </c>
       <c r="U7">
-        <v>0.4987195719777766</v>
+        <v>0.2139607295338708</v>
       </c>
       <c r="V7" t="s">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>1.558293210761144</v>
+        <v>2.684613743554167</v>
       </c>
       <c r="X7">
-        <v>0.08526833542527745</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>0.5269751246641334</v>
+        <v>0.3153862564458332</v>
       </c>
       <c r="Z7">
-        <v>0.04882472535627785</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>0.3017464291168656</v>
+        <v>0.04300958950806959</v>
       </c>
       <c r="AB7">
-        <v>0.7593117840358968</v>
+        <v>0.9166160967040253</v>
       </c>
       <c r="AC7">
-        <v>87.16674245626311</v>
+        <v>98.50593790497011</v>
       </c>
       <c r="AD7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1119,82 +1122,82 @@
         <v>41</v>
       </c>
       <c r="C8">
-        <v>1.076</v>
+        <v>4.108</v>
       </c>
       <c r="D8">
-        <v>1.236</v>
+        <v>3.604</v>
       </c>
       <c r="E8">
-        <v>0.966548112280941</v>
+        <v>4.670106077902364</v>
       </c>
       <c r="F8">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="G8">
-        <v>1.153222778652665</v>
+        <v>3.875948349424152</v>
       </c>
       <c r="J8" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>0.966548112280941</v>
+        <v>3.875948349424152</v>
       </c>
       <c r="L8">
-        <v>0.8200692764238203</v>
+        <v>2.527685652926809</v>
       </c>
       <c r="M8">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N8">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="s">
         <v>42</v>
       </c>
       <c r="P8">
-        <v>0.9850884312991284</v>
+        <v>3.75019908211359</v>
       </c>
       <c r="Q8">
-        <v>1.019181992890591</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.01854031901818742</v>
+        <v>-0.1257492673105625</v>
       </c>
       <c r="U8">
-        <v>0.01491156870087162</v>
+        <v>0.24980091788641</v>
       </c>
       <c r="V8" t="s">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>1.153222778652665</v>
+        <v>3.875948349424152</v>
       </c>
       <c r="X8">
-        <v>0.1866746663717236</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>0.03345188771905905</v>
+        <v>0.1240516505758475</v>
       </c>
       <c r="Z8">
-        <v>0.2276328009577183</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>0.04079153881357063</v>
+        <v>0.0490771668669354</v>
       </c>
       <c r="AB8">
-        <v>0.7455175240216548</v>
+        <v>0.9027448760452889</v>
       </c>
       <c r="AC8">
-        <v>85.02385182059285</v>
+        <v>98.29696753419606</v>
       </c>
       <c r="AD8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:30">
@@ -1205,82 +1208,82 @@
         <v>41</v>
       </c>
       <c r="C9">
-        <v>5.384</v>
+        <v>2.156</v>
       </c>
       <c r="D9">
-        <v>4.436</v>
+        <v>1.984</v>
       </c>
       <c r="E9">
-        <v>4.289783155551396</v>
+        <v>2.747813345994109</v>
       </c>
       <c r="F9">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="G9">
-        <v>4.926455036482963</v>
+        <v>2.076807770041576</v>
       </c>
       <c r="J9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>4.289783155551396</v>
+        <v>2.076807770041576</v>
       </c>
       <c r="L9">
-        <v>2.858585552684069</v>
+        <v>1.513347208585617</v>
       </c>
       <c r="M9">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N9">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="s">
         <v>42</v>
       </c>
       <c r="P9">
-        <v>4.212305297947762</v>
+        <v>2.009428890891545</v>
       </c>
       <c r="Q9">
-        <v>0.981938980411313</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>-0.07747785760363346</v>
+        <v>-0.06737887915003071</v>
       </c>
       <c r="U9">
-        <v>-0.2123052979477622</v>
+        <v>-0.009428890891545194</v>
       </c>
       <c r="V9" t="s">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>4.926455036482963</v>
+        <v>2.076807770041576</v>
       </c>
       <c r="X9">
-        <v>0.6366718809315675</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>0.2897831555513957</v>
+        <v>0.07680777004157591</v>
       </c>
       <c r="Z9">
-        <v>0.2227226959619118</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>0.1013729168536879</v>
+        <v>0.05075356772446217</v>
       </c>
       <c r="AB9">
-        <v>0.6972159884595291</v>
+        <v>0.9458420053660107</v>
       </c>
       <c r="AC9">
-        <v>83.50611917578671</v>
+        <v>98.23930965871645</v>
       </c>
       <c r="AD9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -1288,85 +1291,85 @@
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10">
-        <v>0.6</v>
+        <v>12.34</v>
       </c>
       <c r="D10">
-        <v>0.696</v>
+        <v>10.124</v>
       </c>
       <c r="E10">
-        <v>0.3240271499397565</v>
+        <v>9.224776144749352</v>
       </c>
       <c r="F10">
-        <v>0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G10">
-        <v>0.6451224071145452</v>
+        <v>11.31970940937286</v>
       </c>
       <c r="J10" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>0.3240271499397565</v>
+        <v>11.31970940937286</v>
       </c>
       <c r="L10">
-        <v>1.559831022862906</v>
+        <v>5.707606654863389</v>
       </c>
       <c r="M10">
-        <v>1.038416113387647</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N10">
-        <v>1.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O10" t="s">
         <v>42</v>
       </c>
       <c r="P10">
-        <v>0.2767323416308665</v>
+        <v>10.95245860103622</v>
       </c>
       <c r="Q10">
-        <v>0.8540406002469759</v>
+        <v>0.9675565162447934</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>-0.04729480830888999</v>
+        <v>-0.3672508083366459</v>
       </c>
       <c r="U10">
-        <v>-0.2767323416308665</v>
+        <v>0.04754139896378362</v>
       </c>
       <c r="V10" t="s">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>0.6451224071145452</v>
+        <v>11.31970940937286</v>
       </c>
       <c r="X10">
-        <v>0.3210952571747887</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>0.3240271499397565</v>
+        <v>0.3197094093728623</v>
       </c>
       <c r="Z10">
-        <v>0.2058525907411766</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>0.207732212778432</v>
+        <v>0.05601461850922075</v>
       </c>
       <c r="AB10">
-        <v>1.299859185719089</v>
+        <v>0.6876634523931793</v>
       </c>
       <c r="AC10">
-        <v>81.34177543201334</v>
+        <v>98.05858140436257</v>
       </c>
       <c r="AD10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -1377,82 +1380,82 @@
         <v>41</v>
       </c>
       <c r="C11">
-        <v>3.784</v>
+        <v>9.212</v>
       </c>
       <c r="D11">
-        <v>3.252</v>
+        <v>11.748</v>
       </c>
       <c r="E11">
-        <v>3.656634670288002</v>
+        <v>14.36529697727345</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>13.2</v>
       </c>
       <c r="G11">
-        <v>3.527234260979891</v>
+        <v>10.37962497194514</v>
       </c>
       <c r="J11" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>3.656634670288002</v>
+        <v>10.37962497194514</v>
       </c>
       <c r="L11">
-        <v>0.887818750560327</v>
+        <v>5.848565661247161</v>
       </c>
       <c r="M11">
-        <v>5.24749619700716</v>
+        <v>6.526433735445115</v>
       </c>
       <c r="N11">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O11" t="s">
         <v>42</v>
       </c>
       <c r="P11">
-        <v>3.590592119879259</v>
+        <v>10.77177037254729</v>
       </c>
       <c r="Q11">
-        <v>0.981938980411313</v>
+        <v>1.037780305325296</v>
       </c>
       <c r="R11">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
       </c>
       <c r="T11">
-        <v>-0.06604255040874341</v>
+        <v>0.3921454006021552</v>
       </c>
       <c r="U11">
-        <v>0.409407880120741</v>
+        <v>0.2282296274527074</v>
       </c>
       <c r="V11" t="s">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>3.527234260979891</v>
+        <v>10.37962497194514</v>
       </c>
       <c r="X11">
-        <v>0.1294004093081114</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>0.3433653297119976</v>
+        <v>0.6203750280548626</v>
       </c>
       <c r="Z11">
-        <v>0.1457509308363258</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>0.3867516083607045</v>
+        <v>0.1060730209742695</v>
       </c>
       <c r="AB11">
-        <v>0.3551275002241308</v>
+        <v>0.7132397147862392</v>
       </c>
       <c r="AC11">
-        <v>79.44532252176565</v>
+        <v>96.35551463316079</v>
       </c>
       <c r="AD11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block4_Lowest_Sensitivity_v12.xlsx
+++ b/outputs/Block4_Lowest_Sensitivity_v12.xlsx
@@ -1088,37 +1088,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>44.1233934065934</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="F10" t="n">
-        <v>44.12339340659342</v>
+        <v>44.27542184434272</v>
       </c>
       <c r="G10" t="n">
-        <v>44.16657142857143</v>
+        <v>44.31874863745368</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07847626697110505</v>
+        <v>0.07874665923576957</v>
       </c>
       <c r="J10" t="n">
-        <v>43.99613186813187</v>
+        <v>44.14772182254198</v>
       </c>
       <c r="K10" t="n">
-        <v>44.17793406593407</v>
+        <v>44.33015042511447</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1818021978021989</v>
+        <v>0.1824286025724859</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1272615384615321</v>
+        <v>0.1277000218007345</v>
       </c>
       <c r="N10" t="n">
         <v>1.064148394560983</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1195900300296315</v>
+        <v>0.1200020809629821</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
@@ -1156,37 +1156,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>52.9566065934066</v>
+        <v>52.80457815565729</v>
       </c>
       <c r="F11" t="n">
-        <v>52.9566065934066</v>
+        <v>52.8045781556573</v>
       </c>
       <c r="G11" t="n">
-        <v>53.00842857142858</v>
+        <v>52.85625136254632</v>
       </c>
       <c r="H11" t="n">
         <v>7.105427357601002e-15</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09418669952721606</v>
+        <v>0.09391630726254439</v>
       </c>
       <c r="J11" t="n">
-        <v>52.80386813186814</v>
+        <v>52.65227817745804</v>
       </c>
       <c r="K11" t="n">
-        <v>53.02206593406594</v>
+        <v>52.86984957488554</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2181978021978068</v>
+        <v>0.2175713974275055</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1527384615384619</v>
+        <v>0.1522999781992525</v>
       </c>
       <c r="N11" t="n">
         <v>1.323492690170848</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1154055951142013</v>
+        <v>0.1150742873990428</v>
       </c>
       <c r="P11" t="b">
         <v>1</v>
@@ -1213,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-dd0af9f21104-20261020T060932Z</t>
+          <t>2026-69084551907b-20261024T072445Z</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dd0af9f211044926f193d3ea436dabde2b2960f060ab768c53232e3e59f37c10</t>
+          <t>69084551907b520052181adf33e09563f086f0b6de4f1d95d2e192b06c14159d</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T02:41:23.457320+00:00</t>
+          <t>2026-10-24T07:22:07.989106+00:00</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20T06:09:32.147340+00:00</t>
+          <t>2026-10-24T07:24:45.840036+00:00</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20T06:11:56.240312+00:00</t>
+          <t>2026-10-24T07:26:59.123079+00:00</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>35-race structural motor + polling enrichment on 12 monitored races</t>
+          <t>35-race structural motor + polling enrichment on 15 monitored races</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,53 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Public Senate map highlights 12 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+          <t>Public Senate map highlights 15 monitored races and uses numeric margins for all 35 when v30 is promoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration source</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Recovered Model(5).xlsx / Senate Historic</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration rows</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senate poll-error calibration reference SHA256</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7b3f807a5128485c7fd4de43f99733784af9627e835db4777c047b68e762feb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senate production policy</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Recovered 5B calibration + 15 current monitored races; automatic structural blending disabled</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1702,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-dd0af9f21104-20261020T060932Z</t>
+          <t>2026-69084551907b-20261024T072445Z</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1726,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6254f3f54af6754b67deae4c4b8445dd2c4a92fbbcded33cef106f4df9255f2a</t>
+          <t>8a7bfde9efafe267b78417530287877a5e160939951e8ae39d62138f60d4e05a</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1738,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T06:12:00.987520+00:00</t>
+          <t>2026-10-24T07:27:04.098692+00:00</t>
         </is>
       </c>
     </row>
